--- a/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_Master_Comparison_and_Meta_Analysis.xlsx
+++ b/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_Master_Comparison_and_Meta_Analysis.xlsx
@@ -11615,7 +11615,7 @@
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight_loss' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
+          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight loss &gt;= 5%' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
         </is>
       </c>
     </row>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (weight_loss, waist_circumference, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
+          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (waist_circumference, weight_loss, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
         </is>
       </c>
     </row>
